--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_94_R10.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_94_R10.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.542</v>
+        <v>8.222200000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9457</v>
+        <v>5.2562</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5963</v>
+        <v>2.966</v>
       </c>
       <c r="G2" t="n">
         <v>7.9835</v>
@@ -610,13 +610,13 @@
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6012</v>
+        <v>-0.921</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8057</v>
+        <v>-0.4951</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7956</v>
+        <v>-0.4259</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0233</v>
+        <v>4.9457</v>
       </c>
       <c r="E3" t="n">
-        <v>3.131</v>
+        <v>2.8518</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8923</v>
+        <v>2.0939</v>
       </c>
       <c r="G3" t="n">
         <v>4.4604</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3829</v>
+        <v>-1.4605</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7073</v>
+        <v>-0.9865</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6756</v>
+        <v>-0.474</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1418</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8919</v>
+        <v>2.7485</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3737</v>
+        <v>1.5663</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5182</v>
+        <v>1.1821</v>
       </c>
       <c r="G4" t="n">
         <v>4.4593</v>
@@ -766,13 +766,13 @@
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8689</v>
+        <v>-1.0124</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.7924</v>
+        <v>-1.5997</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9234</v>
+        <v>0.5874</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9304</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9595</v>
+        <v>2.0621</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.6052</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5647</v>
+        <v>2.6967</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4562</v>
+        <v>1.2769</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0241</v>
+        <v>1.5714</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4321</v>
+        <v>-0.2946</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0701</v>
+        <v>0.2547</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7191</v>
+        <v>0.8605</v>
       </c>
       <c r="L5" t="n">
-        <v>0.649</v>
+        <v>-0.6058</v>
       </c>
       <c r="M5" t="n">
-        <v>1.5263</v>
+        <v>1.0222</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7432</v>
+        <v>0.7109</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7831</v>
+        <v>0.3113</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6237</v>
+        <v>2.3195</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4736</v>
+        <v>-0.3745</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8883</v>
+        <v>-0.8017</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4147</v>
+        <v>0.4272</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6468</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6468</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5163</v>
+        <v>1.6309</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9452</v>
+        <v>-1.5305</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4614</v>
+        <v>3.1614</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2769</v>
+        <v>1.4562</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5714</v>
+        <v>0.0241</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2946</v>
+        <v>1.4321</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2547</v>
+        <v>-0.0701</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8605</v>
+        <v>-0.7191</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6058</v>
+        <v>0.649</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0222</v>
+        <v>1.5263</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7109</v>
+        <v>0.7432</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3113</v>
+        <v>0.7831</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9203</v>
+        <v>-0.8022</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1123</v>
+        <v>-0.8136</v>
       </c>
       <c r="U6" t="n">
-        <v>0.192</v>
+        <v>0.0114</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.6468</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>-0.6468</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7043</v>
+        <v>1.2337</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0987</v>
+        <v>-1.6702</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8031</v>
+        <v>2.9039</v>
       </c>
       <c r="G7" t="n">
         <v>1.1577</v>
@@ -1000,13 +1000,13 @@
         <v>2.5515</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1672</v>
+        <v>-0.6379</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.4031</v>
+        <v>-0.9746</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2359</v>
+        <v>0.3367</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6778999999999999</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0569</v>
+        <v>0.3002</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8855</v>
+        <v>-2.5749</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9423</v>
+        <v>2.8751</v>
       </c>
       <c r="G8" t="n">
         <v>-0.96</v>
@@ -1078,13 +1078,13 @@
         <v>2.3195</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2847</v>
+        <v>-0.0413</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1791</v>
+        <v>-0.8685</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8944</v>
+        <v>0.8272</v>
       </c>
       <c r="V8" t="n">
         <v>0.1418</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3694</v>
+        <v>-0.3022</v>
       </c>
       <c r="E9" t="n">
         <v>-1.2457</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8764</v>
+        <v>0.9436</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3395</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7257</v>
+        <v>-0.6585</v>
       </c>
       <c r="T9" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.427</v>
+        <v>-0.3598</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8878</v>
+        <v>-0.4935</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6394</v>
+        <v>-0.4467</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2484</v>
+        <v>-0.0467</v>
       </c>
       <c r="G10" t="n">
         <v>0.3357</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2415</v>
+        <v>-0.8472</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8215</v>
+        <v>-0.6289</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.42</v>
+        <v>-0.2183</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6778999999999999</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0345</v>
+        <v>-1.3295</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5465</v>
+        <v>0.6212</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.581</v>
+        <v>-1.9507</v>
       </c>
       <c r="G11" t="n">
         <v>0.7000999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.054</v>
+        <v>-0.349</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7468</v>
+        <v>-0.6721</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6928</v>
+        <v>0.3231</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1444</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0838</v>
+        <v>-2.3465</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2646</v>
+        <v>-3.6617</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1808</v>
+        <v>1.3152</v>
       </c>
       <c r="G12" t="n">
         <v>0.8005</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1369</v>
+        <v>-1.3996</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3339</v>
+        <v>-0.731</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.803</v>
+        <v>-0.6686</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8197</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.7845</v>
+        <v>-4.3908</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2799</v>
+        <v>-3.7517</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5046</v>
+        <v>-0.639</v>
       </c>
       <c r="G13" t="n">
         <v>0.7897</v>
@@ -1468,13 +1468,13 @@
         <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9129</v>
+        <v>0.3066</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2047</v>
+        <v>-0.2671</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7082000000000001</v>
+        <v>0.5737</v>
       </c>
       <c r="V13" t="n">
         <v>-3.8634</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.5342</v>
+        <v>12.2808</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.9673</v>
+        <v>-5.2205</v>
       </c>
       <c r="F14" t="n">
         <v>17.5015</v>
@@ -1522,10 +1522,10 @@
         <v>10.54</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7548000000000005</v>
+        <v>0.7548000000000007</v>
       </c>
       <c r="L14" t="n">
-        <v>9.785199999999998</v>
+        <v>9.7852</v>
       </c>
       <c r="M14" t="n">
         <v>11.5807</v>
@@ -1546,13 +1546,13 @@
         <v>18.5563</v>
       </c>
       <c r="S14" t="n">
-        <v>-8.944000000000001</v>
+        <v>-8.1975</v>
       </c>
       <c r="T14" t="n">
-        <v>-9.884399999999999</v>
+        <v>-9.137499999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9401999999999999</v>
+        <v>0.9401000000000004</v>
       </c>
       <c r="V14" t="n">
         <v>-9.7605</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8445</v>
+        <v>5.3379</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2018</v>
+        <v>3.1454</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6428</v>
+        <v>2.1925</v>
       </c>
       <c r="G15" t="n">
         <v>-2.0628</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9871</v>
+        <v>0.5063</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.7098</v>
+        <v>-0.7662</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7227</v>
+        <v>1.2724</v>
       </c>
       <c r="V15" t="n">
         <v>5.5028</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.965</v>
+        <v>1.8369</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7141</v>
+        <v>0.8884</v>
       </c>
       <c r="F16" t="n">
-        <v>1.251</v>
+        <v>0.9485</v>
       </c>
       <c r="G16" t="n">
         <v>-2.4545</v>
@@ -1702,13 +1702,13 @@
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>3.2029</v>
+        <v>2.0748</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3293</v>
+        <v>0.5036</v>
       </c>
       <c r="U16" t="n">
-        <v>1.8736</v>
+        <v>1.5712</v>
       </c>
       <c r="V16" t="n">
         <v>2.6805</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1638</v>
+        <v>0.8036</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0359</v>
+        <v>2.5077</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8722</v>
+        <v>-1.7041</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3404</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8237</v>
+        <v>1.4635</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2434</v>
+        <v>0.2284</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0671</v>
+        <v>1.2351</v>
       </c>
       <c r="V17" t="n">
         <v>1.0722</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0699</v>
+        <v>-0.3657</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3189</v>
+        <v>-1.6197</v>
       </c>
       <c r="F18" t="n">
-        <v>1.249</v>
+        <v>1.254</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4994</v>
+        <v>-1.6675</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2448</v>
+        <v>-1.7179</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2546</v>
+        <v>0.0504</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3955</v>
+        <v>-0.8706</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1478</v>
+        <v>-0.981</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.2477</v>
+        <v>0.1104</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1039</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.097</v>
+        <v>-0.7369</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0069</v>
+        <v>-0.06</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1253</v>
+        <v>0.9976</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4683</v>
+        <v>0.1065</v>
       </c>
       <c r="U18" t="n">
-        <v>1.657</v>
+        <v>0.8911</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2453</v>
+        <v>-0.3731</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.391</v>
+        <v>-1.5548</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1457</v>
+        <v>1.1817</v>
       </c>
       <c r="G19" t="n">
-        <v>0.024</v>
+        <v>-1.4994</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3218</v>
+        <v>-0.2448</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2978</v>
+        <v>-1.2546</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2812</v>
+        <v>-0.3955</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0504</v>
+        <v>-0.1478</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2308</v>
+        <v>-0.2477</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2572</v>
+        <v>-1.1039</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2714</v>
+        <v>-0.097</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5286</v>
+        <v>-1.0069</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1598</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8905</v>
+        <v>1.8222</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4876</v>
+        <v>0.2324</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4028</v>
+        <v>1.5898</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4272</v>
+        <v>-0.4311</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2658</v>
+        <v>-0.7448</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8386</v>
+        <v>0.3137</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6675</v>
+        <v>0.024</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7179</v>
+        <v>0.3218</v>
       </c>
       <c r="I20" t="n">
+        <v>-0.2978</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="K20" t="n">
         <v>0.0504</v>
       </c>
-      <c r="J20" t="n">
-        <v>-0.8706</v>
-      </c>
-      <c r="K20" t="n">
-        <v>-0.981</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.1104</v>
+        <v>0.2308</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-0.2572</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7369</v>
+        <v>0.2714</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.06</v>
+        <v>-0.5286</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9361</v>
+        <v>0.7046</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4604</v>
+        <v>0.1338</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4758</v>
+        <v>0.5709</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7897999999999999</v>
+        <v>-1.0485</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4035</v>
+        <v>-3.1112</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6137</v>
+        <v>2.0627</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6815</v>
@@ -2092,13 +2092,13 @@
         <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8918</v>
+        <v>0.633</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5272</v>
+        <v>-0.1806</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3646</v>
+        <v>0.8136</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2745</v>
+        <v>-2.7899</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8292</v>
+        <v>-2.2042</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5547</v>
+        <v>-0.5858</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.9475</v>
+        <v>-2.7083</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0577</v>
+        <v>-1.4034</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.0052</v>
+        <v>-1.3049</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.0077</v>
+        <v>-1.7365</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1008</v>
+        <v>-1.5391</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.1086</v>
+        <v>-0.1975</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9398</v>
+        <v>-0.9717</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0431</v>
+        <v>0.1357</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8966</v>
+        <v>-1.1074</v>
       </c>
       <c r="P22" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4411</v>
+        <v>-0.0275</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5895</v>
+        <v>-0.4676</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0306</v>
+        <v>0.4402</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5928</v>
+        <v>-2.9371</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.558</v>
+        <v>-3.3574</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0347</v>
+        <v>0.4203</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.7083</v>
+        <v>-3.9475</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4034</v>
+        <v>0.0577</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3049</v>
+        <v>-4.0052</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.7365</v>
+        <v>-3.0077</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5391</v>
+        <v>0.1008</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.1975</v>
+        <v>-3.1086</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9717</v>
+        <v>-0.9398</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1357</v>
+        <v>-0.0431</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1074</v>
+        <v>-0.8966</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8303</v>
+        <v>0.7784</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8215</v>
+        <v>-0.1177</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.8962</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6093</v>
+        <v>-4.6815</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.9503</v>
+        <v>-6.0682</v>
       </c>
       <c r="F24" t="n">
-        <v>1.341</v>
+        <v>1.3867</v>
       </c>
       <c r="G24" t="n">
         <v>-4.2752</v>
@@ -2326,13 +2326,13 @@
         <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6581</v>
+        <v>0.5858</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1845</v>
+        <v>-0.3025</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8426</v>
+        <v>0.8883</v>
       </c>
       <c r="V24" t="n">
         <v>2.2551</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.4987</v>
+        <v>-5.3129</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.7365</v>
+        <v>-5.3827</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2379</v>
+        <v>0.0698</v>
       </c>
       <c r="G25" t="n">
         <v>-1.5073</v>
@@ -2404,13 +2404,13 @@
         <v>0.9278</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7921</v>
+        <v>0.9779</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6642</v>
+        <v>-0.3104</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4563</v>
+        <v>1.2883</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-11.5342</v>
+        <v>-9.961399999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-17.5014</v>
+        <v>-17.5015</v>
       </c>
       <c r="F26" t="n">
-        <v>5.9675</v>
+        <v>7.54</v>
       </c>
       <c r="G26" t="n">
         <v>-22.1204</v>
@@ -2473,7 +2473,7 @@
         <v>-9.7852</v>
       </c>
       <c r="P26" t="n">
-        <v>-8.118300000000001</v>
+        <v>-8.1183</v>
       </c>
       <c r="Q26" t="n">
         <v>-18.5562</v>
@@ -2482,13 +2482,13 @@
         <v>10.438</v>
       </c>
       <c r="S26" t="n">
-        <v>8.9442</v>
+        <v>10.5166</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9401000000000002</v>
+        <v>-0.9403</v>
       </c>
       <c r="U26" t="n">
-        <v>9.8843</v>
+        <v>11.4571</v>
       </c>
       <c r="V26" t="n">
         <v>9.760499999999999</v>
